--- a/www/terminologies/ValueSet-JDV-J106-EnsembleProfession-RASS.xlsx
+++ b/www/terminologies/ValueSet-JDV-J106-EnsembleProfession-RASS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250328120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-28T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -154,12 +154,6 @@
   </si>
   <si>
     <t>Infirmier</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>Infirmier psychiatrique</t>
   </si>
   <si>
     <t>70</t>
@@ -559,7 +553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -763,23 +757,15 @@
         <v>74</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>76</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -806,50 +792,50 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -876,26 +862,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -922,26 +908,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
